--- a/samples/示例-网格型课表.xlsx
+++ b/samples/示例-网格型课表.xlsx
@@ -513,7 +513,7 @@
         <v>第2节</v>
       </c>
       <c r="B4" t="str">
-        <v>08:55-09:40</v>
+        <v>08:50-09:35</v>
       </c>
       <c r="C4" t="str">
         <v/>
@@ -542,7 +542,7 @@
         <v>第3节</v>
       </c>
       <c r="B5" t="str">
-        <v>10:00-10:45</v>
+        <v>09:50-10:35</v>
       </c>
       <c r="C5" t="str" xml:space="preserve">
         <v xml:space="preserve">大学英语
@@ -575,7 +575,7 @@
         <v>第4节</v>
       </c>
       <c r="B6" t="str">
-        <v>10:55-11:40</v>
+        <v>10:40-11:25</v>
       </c>
       <c r="C6" t="str">
         <v/>
@@ -642,7 +642,7 @@
         <v>第6节</v>
       </c>
       <c r="B8" t="str">
-        <v>14:55-15:40</v>
+        <v>14:50-15:35</v>
       </c>
       <c r="C8" t="str">
         <v/>
@@ -671,7 +671,7 @@
         <v>第7节</v>
       </c>
       <c r="B9" t="str">
-        <v>16:00-16:45</v>
+        <v>15:50-16:35</v>
       </c>
       <c r="C9" t="str" xml:space="preserve">
         <v xml:space="preserve">体育（羽毛球）
@@ -704,7 +704,7 @@
         <v>第8节</v>
       </c>
       <c r="B10" t="str">
-        <v>16:55-17:40</v>
+        <v>16:40-17:25</v>
       </c>
       <c r="C10" t="str">
         <v/>
@@ -733,7 +733,7 @@
         <v>第9节</v>
       </c>
       <c r="B11" t="str">
-        <v>19:00-19:45</v>
+        <v>18:00-18:45</v>
       </c>
       <c r="C11" t="str">
         <v/>
@@ -764,7 +764,7 @@
         <v>第10节</v>
       </c>
       <c r="B12" t="str">
-        <v>19:55-20:40</v>
+        <v>18:50-19:35</v>
       </c>
       <c r="C12" t="str">
         <v/>
